--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ166"/>
+  <dimension ref="A1:AZ168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3602,10 +3602,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129542956</v>
+        <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>81312</v>
+        <v>79598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>967</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457662</v>
+        <v>457985</v>
       </c>
       <c r="R28" t="n">
-        <v>6748216</v>
+        <v>6748592</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3667,22 +3667,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Känd förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,13 +3713,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542956</t>
+          <t>https://artportalen.se/Sighting/137251099</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129542957</v>
+        <v>129542956</v>
       </c>
       <c r="B29" t="n">
         <v>81312</v>
@@ -3749,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457986</v>
+        <v>457662</v>
       </c>
       <c r="R29" t="n">
-        <v>6748595</v>
+        <v>6748216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3794,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3820,13 +3825,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542957</t>
+          <t>https://artportalen.se/Sighting/129542956</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129542958</v>
+        <v>129542957</v>
       </c>
       <c r="B30" t="n">
         <v>81312</v>
@@ -3861,10 +3866,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458029</v>
+        <v>457986</v>
       </c>
       <c r="R30" t="n">
-        <v>6748402</v>
+        <v>6748595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3896,7 +3901,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3906,7 +3911,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,13 +3937,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542958</t>
+          <t>https://artportalen.se/Sighting/129542957</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129542959</v>
+        <v>129542958</v>
       </c>
       <c r="B31" t="n">
         <v>81312</v>
@@ -3973,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457884</v>
+        <v>458029</v>
       </c>
       <c r="R31" t="n">
-        <v>6748404</v>
+        <v>6748402</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4008,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4018,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4044,16 +4049,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542959</t>
+          <t>https://artportalen.se/Sighting/129542958</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129542924</v>
+        <v>129542959</v>
       </c>
       <c r="B32" t="n">
-        <v>91909</v>
+        <v>81312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,21 +4066,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457899</v>
+        <v>457884</v>
       </c>
       <c r="R32" t="n">
-        <v>6748444</v>
+        <v>6748404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,7 +4125,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4135,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,38 +4161,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542924</t>
+          <t>https://artportalen.se/Sighting/129542959</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129542980</v>
+        <v>129542924</v>
       </c>
       <c r="B33" t="n">
-        <v>92083</v>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4197,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458058</v>
+        <v>457899</v>
       </c>
       <c r="R33" t="n">
-        <v>6748621</v>
+        <v>6748444</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4237,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,7 +4247,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4268,13 +4273,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542980</t>
+          <t>https://artportalen.se/Sighting/129542924</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129542981</v>
+        <v>129542980</v>
       </c>
       <c r="B34" t="n">
         <v>92083</v>
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457964</v>
+        <v>458058</v>
       </c>
       <c r="R34" t="n">
-        <v>6748415</v>
+        <v>6748621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4344,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4359,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,38 +4385,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542981</t>
+          <t>https://artportalen.se/Sighting/129542980</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129542946</v>
+        <v>129542981</v>
       </c>
       <c r="B35" t="n">
-        <v>91962</v>
+        <v>92083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4421,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458035</v>
+        <v>457964</v>
       </c>
       <c r="R35" t="n">
-        <v>6748395</v>
+        <v>6748415</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,38 +4497,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542946</t>
+          <t>https://artportalen.se/Sighting/129542981</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543112</v>
+        <v>129542946</v>
       </c>
       <c r="B36" t="n">
-        <v>91966</v>
+        <v>91962</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5321</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4538,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458029</v>
+        <v>458035</v>
       </c>
       <c r="R36" t="n">
-        <v>6748411</v>
+        <v>6748395</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4568,7 +4573,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4583,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4587,7 +4592,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4605,16 +4609,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543112</t>
+          <t>https://artportalen.se/Sighting/129542946</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129542920</v>
+        <v>129543112</v>
       </c>
       <c r="B37" t="n">
-        <v>91872</v>
+        <v>91966</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4622,21 +4626,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>5321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4646,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457964</v>
+        <v>458029</v>
       </c>
       <c r="R37" t="n">
-        <v>6748415</v>
+        <v>6748411</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,7 +4685,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4695,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4700,6 +4704,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4717,38 +4722,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542920</t>
+          <t>https://artportalen.se/Sighting/129543112</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129542955</v>
+        <v>129542920</v>
       </c>
       <c r="B38" t="n">
-        <v>92556</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5454</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4758,10 +4763,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>458015</v>
+        <v>457964</v>
       </c>
       <c r="R38" t="n">
-        <v>6748399</v>
+        <v>6748415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4793,7 +4798,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4808,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4829,38 +4834,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542955</t>
+          <t>https://artportalen.se/Sighting/129542920</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129542978</v>
+        <v>129542955</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>92556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4870,10 +4875,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457802</v>
+        <v>458015</v>
       </c>
       <c r="R39" t="n">
-        <v>6748301</v>
+        <v>6748399</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4905,7 +4910,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4920,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4941,13 +4946,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542978</t>
+          <t>https://artportalen.se/Sighting/129542955</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129542982</v>
+        <v>129542978</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4982,10 +4987,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457941</v>
+        <v>457802</v>
       </c>
       <c r="R40" t="n">
-        <v>6748477</v>
+        <v>6748301</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5017,7 +5022,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5027,12 +5032,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På undertryckt gran som röjts</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,13 +5058,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542982</t>
+          <t>https://artportalen.se/Sighting/129542978</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129542991</v>
+        <v>129542982</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457762</v>
+        <v>457941</v>
       </c>
       <c r="R41" t="n">
-        <v>6748312</v>
+        <v>6748477</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5144,7 +5144,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På undertryckt gran som röjts</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,13 +5175,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542991</t>
+          <t>https://artportalen.se/Sighting/129542982</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129542992</v>
+        <v>129542991</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5211,10 +5216,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457763</v>
+        <v>457762</v>
       </c>
       <c r="R42" t="n">
-        <v>6748301</v>
+        <v>6748312</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5282,13 +5287,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542992</t>
+          <t>https://artportalen.se/Sighting/129542991</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129542993</v>
+        <v>129542992</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5326,7 +5331,7 @@
         <v>457763</v>
       </c>
       <c r="R43" t="n">
-        <v>6748294</v>
+        <v>6748301</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5394,13 +5399,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542993</t>
+          <t>https://artportalen.se/Sighting/129542992</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129542994</v>
+        <v>129542993</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5435,10 +5440,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457786</v>
+        <v>457763</v>
       </c>
       <c r="R44" t="n">
-        <v>6748280</v>
+        <v>6748294</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5470,7 +5475,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5480,7 +5485,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5506,13 +5511,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542994</t>
+          <t>https://artportalen.se/Sighting/129542993</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129542995</v>
+        <v>129542994</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5547,10 +5552,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457809</v>
+        <v>457786</v>
       </c>
       <c r="R45" t="n">
-        <v>6748246</v>
+        <v>6748280</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5582,7 +5587,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5592,7 +5597,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5618,13 +5623,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542995</t>
+          <t>https://artportalen.se/Sighting/129542994</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129542996</v>
+        <v>129542995</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5659,10 +5664,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457833</v>
+        <v>457809</v>
       </c>
       <c r="R46" t="n">
-        <v>6748233</v>
+        <v>6748246</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5730,13 +5735,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542996</t>
+          <t>https://artportalen.se/Sighting/129542995</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129542997</v>
+        <v>129542996</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5771,10 +5776,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457863</v>
+        <v>457833</v>
       </c>
       <c r="R47" t="n">
-        <v>6748231</v>
+        <v>6748233</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5806,7 +5811,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5816,7 +5821,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5842,13 +5847,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542997</t>
+          <t>https://artportalen.se/Sighting/129542996</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129542998</v>
+        <v>129542997</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5883,10 +5888,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457876</v>
+        <v>457863</v>
       </c>
       <c r="R48" t="n">
-        <v>6748240</v>
+        <v>6748231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5918,7 +5923,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5928,7 +5933,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5954,13 +5959,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542998</t>
+          <t>https://artportalen.se/Sighting/129542997</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129542999</v>
+        <v>129542998</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5995,10 +6000,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457883</v>
+        <v>457876</v>
       </c>
       <c r="R49" t="n">
-        <v>6748260</v>
+        <v>6748240</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6030,7 +6035,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6040,7 +6045,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6066,13 +6071,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542999</t>
+          <t>https://artportalen.se/Sighting/129542998</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129543000</v>
+        <v>129542999</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -6107,10 +6112,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457846</v>
+        <v>457883</v>
       </c>
       <c r="R50" t="n">
-        <v>6748214</v>
+        <v>6748260</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6142,7 +6147,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6152,7 +6157,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6178,13 +6183,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543000</t>
+          <t>https://artportalen.se/Sighting/129542999</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129543001</v>
+        <v>129543000</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6219,10 +6224,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457838</v>
+        <v>457846</v>
       </c>
       <c r="R51" t="n">
-        <v>6748208</v>
+        <v>6748214</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6254,7 +6259,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6264,7 +6269,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6290,13 +6295,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543001</t>
+          <t>https://artportalen.se/Sighting/129543000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129543002</v>
+        <v>129543001</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6331,10 +6336,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457813</v>
+        <v>457838</v>
       </c>
       <c r="R52" t="n">
-        <v>6748191</v>
+        <v>6748208</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6402,13 +6407,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543002</t>
+          <t>https://artportalen.se/Sighting/129543001</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129543003</v>
+        <v>129543002</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6443,10 +6448,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457814</v>
+        <v>457813</v>
       </c>
       <c r="R53" t="n">
-        <v>6748175</v>
+        <v>6748191</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6478,7 +6483,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6488,7 +6493,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6514,13 +6519,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543003</t>
+          <t>https://artportalen.se/Sighting/129543002</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129543004</v>
+        <v>129543003</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6555,10 +6560,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457802</v>
+        <v>457814</v>
       </c>
       <c r="R54" t="n">
-        <v>6748157</v>
+        <v>6748175</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6626,13 +6631,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543004</t>
+          <t>https://artportalen.se/Sighting/129543003</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129543005</v>
+        <v>129543004</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457775</v>
+        <v>457802</v>
       </c>
       <c r="R55" t="n">
-        <v>6748148</v>
+        <v>6748157</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6702,7 +6707,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6712,7 +6717,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6738,13 +6743,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543005</t>
+          <t>https://artportalen.se/Sighting/129543004</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129543006</v>
+        <v>129543005</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6779,10 +6784,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457712</v>
+        <v>457775</v>
       </c>
       <c r="R56" t="n">
-        <v>6748081</v>
+        <v>6748148</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6814,7 +6819,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6824,7 +6829,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6850,13 +6855,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543006</t>
+          <t>https://artportalen.se/Sighting/129543005</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129543007</v>
+        <v>129543006</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6891,10 +6896,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457677</v>
+        <v>457712</v>
       </c>
       <c r="R57" t="n">
-        <v>6748051</v>
+        <v>6748081</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6926,7 +6931,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6936,7 +6941,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6962,13 +6967,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543007</t>
+          <t>https://artportalen.se/Sighting/129543006</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129543008</v>
+        <v>129543007</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -7003,10 +7008,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457671</v>
+        <v>457677</v>
       </c>
       <c r="R58" t="n">
-        <v>6748048</v>
+        <v>6748051</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7038,7 +7043,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7048,7 +7053,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7074,13 +7079,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543008</t>
+          <t>https://artportalen.se/Sighting/129543007</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129543009</v>
+        <v>129543008</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -7115,10 +7120,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457654</v>
+        <v>457671</v>
       </c>
       <c r="R59" t="n">
-        <v>6748079</v>
+        <v>6748048</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7150,7 +7155,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7160,7 +7165,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7186,13 +7191,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543009</t>
+          <t>https://artportalen.se/Sighting/129543008</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129543010</v>
+        <v>129543009</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7227,10 +7232,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457656</v>
+        <v>457654</v>
       </c>
       <c r="R60" t="n">
-        <v>6748084</v>
+        <v>6748079</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7262,7 +7267,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7272,7 +7277,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7298,13 +7303,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543010</t>
+          <t>https://artportalen.se/Sighting/129543009</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129543011</v>
+        <v>129543010</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7339,10 +7344,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457665</v>
+        <v>457656</v>
       </c>
       <c r="R61" t="n">
-        <v>6748082</v>
+        <v>6748084</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7410,13 +7415,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543011</t>
+          <t>https://artportalen.se/Sighting/129543010</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129543012</v>
+        <v>129543011</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -7451,10 +7456,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457625</v>
+        <v>457665</v>
       </c>
       <c r="R62" t="n">
-        <v>6748127</v>
+        <v>6748082</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7486,7 +7491,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7496,7 +7501,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7522,13 +7527,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543012</t>
+          <t>https://artportalen.se/Sighting/129543011</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129543013</v>
+        <v>129543012</v>
       </c>
       <c r="B63" t="n">
         <v>79327</v>
@@ -7563,10 +7568,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457621</v>
+        <v>457625</v>
       </c>
       <c r="R63" t="n">
-        <v>6748147</v>
+        <v>6748127</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7598,7 +7603,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7608,7 +7613,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7634,13 +7639,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543013</t>
+          <t>https://artportalen.se/Sighting/129543012</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129543014</v>
+        <v>129543013</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7675,10 +7680,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457634</v>
+        <v>457621</v>
       </c>
       <c r="R64" t="n">
-        <v>6748179</v>
+        <v>6748147</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7710,7 +7715,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7720,7 +7725,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7746,13 +7751,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543014</t>
+          <t>https://artportalen.se/Sighting/129543013</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129543015</v>
+        <v>129543014</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7787,10 +7792,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457689</v>
+        <v>457634</v>
       </c>
       <c r="R65" t="n">
-        <v>6748165</v>
+        <v>6748179</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7822,7 +7827,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7832,7 +7837,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7858,13 +7863,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543015</t>
+          <t>https://artportalen.se/Sighting/129543014</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129543016</v>
+        <v>129543015</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7899,10 +7904,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457699</v>
+        <v>457689</v>
       </c>
       <c r="R66" t="n">
-        <v>6748197</v>
+        <v>6748165</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7934,7 +7939,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7944,7 +7949,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7970,13 +7975,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543016</t>
+          <t>https://artportalen.se/Sighting/129543015</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129543017</v>
+        <v>129543016</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -8011,10 +8016,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457657</v>
+        <v>457699</v>
       </c>
       <c r="R67" t="n">
-        <v>6748226</v>
+        <v>6748197</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8046,7 +8051,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8056,7 +8061,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8082,13 +8087,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543017</t>
+          <t>https://artportalen.se/Sighting/129543016</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129543018</v>
+        <v>129543017</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -8123,10 +8128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457679</v>
+        <v>457657</v>
       </c>
       <c r="R68" t="n">
-        <v>6748231</v>
+        <v>6748226</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8194,13 +8199,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543018</t>
+          <t>https://artportalen.se/Sighting/129543017</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129543019</v>
+        <v>129543018</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -8235,10 +8240,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457725</v>
+        <v>457679</v>
       </c>
       <c r="R69" t="n">
-        <v>6748208</v>
+        <v>6748231</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8275,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,7 +8285,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8306,13 +8311,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543019</t>
+          <t>https://artportalen.se/Sighting/129543018</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129543020</v>
+        <v>129543019</v>
       </c>
       <c r="B70" t="n">
         <v>79327</v>
@@ -8347,10 +8352,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457738</v>
+        <v>457725</v>
       </c>
       <c r="R70" t="n">
-        <v>6748205</v>
+        <v>6748208</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8418,13 +8423,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543020</t>
+          <t>https://artportalen.se/Sighting/129543019</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129543021</v>
+        <v>129543020</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8459,10 +8464,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457756</v>
+        <v>457738</v>
       </c>
       <c r="R71" t="n">
-        <v>6748192</v>
+        <v>6748205</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8494,7 +8499,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8504,7 +8509,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8530,13 +8535,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543021</t>
+          <t>https://artportalen.se/Sighting/129543020</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129543022</v>
+        <v>129543021</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8571,7 +8576,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457761</v>
+        <v>457756</v>
       </c>
       <c r="R72" t="n">
         <v>6748192</v>
@@ -8642,13 +8647,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543022</t>
+          <t>https://artportalen.se/Sighting/129543021</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129543023</v>
+        <v>129543022</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8683,10 +8688,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457758</v>
+        <v>457761</v>
       </c>
       <c r="R73" t="n">
-        <v>6748213</v>
+        <v>6748192</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8718,7 +8723,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8728,7 +8733,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8754,13 +8759,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543023</t>
+          <t>https://artportalen.se/Sighting/129543022</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129543024</v>
+        <v>129543023</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8795,10 +8800,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457755</v>
+        <v>457758</v>
       </c>
       <c r="R74" t="n">
-        <v>6748219</v>
+        <v>6748213</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,13 +8871,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543024</t>
+          <t>https://artportalen.se/Sighting/129543023</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129543025</v>
+        <v>129543024</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8907,10 +8912,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457761</v>
+        <v>457755</v>
       </c>
       <c r="R75" t="n">
-        <v>6748254</v>
+        <v>6748219</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8942,7 +8947,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8952,7 +8957,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8978,13 +8983,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543025</t>
+          <t>https://artportalen.se/Sighting/129543024</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129543026</v>
+        <v>129543025</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -9019,10 +9024,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457758</v>
+        <v>457761</v>
       </c>
       <c r="R76" t="n">
-        <v>6748263</v>
+        <v>6748254</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9090,13 +9095,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543026</t>
+          <t>https://artportalen.se/Sighting/129543025</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129543027</v>
+        <v>129543026</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -9131,10 +9136,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457756</v>
+        <v>457758</v>
       </c>
       <c r="R77" t="n">
-        <v>6748271</v>
+        <v>6748263</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9202,13 +9207,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543027</t>
+          <t>https://artportalen.se/Sighting/129543026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129543028</v>
+        <v>129543027</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -9243,10 +9248,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457753</v>
+        <v>457756</v>
       </c>
       <c r="R78" t="n">
-        <v>6748290</v>
+        <v>6748271</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9278,7 +9283,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9288,7 +9293,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9314,13 +9319,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543028</t>
+          <t>https://artportalen.se/Sighting/129543027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129543029</v>
+        <v>129543028</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -9355,10 +9360,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457780</v>
+        <v>457753</v>
       </c>
       <c r="R79" t="n">
-        <v>6748311</v>
+        <v>6748290</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9390,7 +9395,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9400,7 +9405,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9426,13 +9431,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543029</t>
+          <t>https://artportalen.se/Sighting/129543028</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129543030</v>
+        <v>129543029</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9467,10 +9472,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457811</v>
+        <v>457780</v>
       </c>
       <c r="R80" t="n">
-        <v>6748293</v>
+        <v>6748311</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9502,7 +9507,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9512,7 +9517,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9538,13 +9543,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543030</t>
+          <t>https://artportalen.se/Sighting/129543029</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129543031</v>
+        <v>129543030</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9579,10 +9584,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457809</v>
+        <v>457811</v>
       </c>
       <c r="R81" t="n">
-        <v>6748286</v>
+        <v>6748293</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9650,13 +9655,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543031</t>
+          <t>https://artportalen.se/Sighting/129543030</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129543032</v>
+        <v>129543031</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9691,10 +9696,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457821</v>
+        <v>457809</v>
       </c>
       <c r="R82" t="n">
-        <v>6748297</v>
+        <v>6748286</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9762,13 +9767,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543032</t>
+          <t>https://artportalen.se/Sighting/129543031</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129543033</v>
+        <v>129543032</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9803,10 +9808,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457836</v>
+        <v>457821</v>
       </c>
       <c r="R83" t="n">
-        <v>6748291</v>
+        <v>6748297</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9838,7 +9843,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9848,7 +9853,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9874,13 +9879,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543033</t>
+          <t>https://artportalen.se/Sighting/129543032</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129543034</v>
+        <v>129543033</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9915,10 +9920,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457852</v>
+        <v>457836</v>
       </c>
       <c r="R84" t="n">
-        <v>6748316</v>
+        <v>6748291</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9986,13 +9991,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543034</t>
+          <t>https://artportalen.se/Sighting/129543033</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129543035</v>
+        <v>129543034</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -10027,10 +10032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>457845</v>
+        <v>457852</v>
       </c>
       <c r="R85" t="n">
-        <v>6748327</v>
+        <v>6748316</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10062,7 +10067,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10072,7 +10077,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10098,13 +10103,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543035</t>
+          <t>https://artportalen.se/Sighting/129543034</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129543036</v>
+        <v>129543035</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -10139,10 +10144,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457843</v>
+        <v>457845</v>
       </c>
       <c r="R86" t="n">
-        <v>6748341</v>
+        <v>6748327</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10210,13 +10215,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543036</t>
+          <t>https://artportalen.se/Sighting/129543035</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129543037</v>
+        <v>129543036</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -10251,10 +10256,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457830</v>
+        <v>457843</v>
       </c>
       <c r="R87" t="n">
-        <v>6748350</v>
+        <v>6748341</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10286,7 +10291,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10296,7 +10301,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10322,13 +10327,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543037</t>
+          <t>https://artportalen.se/Sighting/129543036</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129543038</v>
+        <v>129543037</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -10363,10 +10368,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457829</v>
+        <v>457830</v>
       </c>
       <c r="R88" t="n">
-        <v>6748366</v>
+        <v>6748350</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10398,7 +10403,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10408,7 +10413,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10434,13 +10439,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543038</t>
+          <t>https://artportalen.se/Sighting/129543037</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129543039</v>
+        <v>129543038</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -10475,10 +10480,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457830</v>
+        <v>457829</v>
       </c>
       <c r="R89" t="n">
-        <v>6748402</v>
+        <v>6748366</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10510,7 +10515,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10520,7 +10525,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10546,13 +10551,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543039</t>
+          <t>https://artportalen.se/Sighting/129543038</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129543040</v>
+        <v>129543039</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10587,10 +10592,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457817</v>
+        <v>457830</v>
       </c>
       <c r="R90" t="n">
-        <v>6748400</v>
+        <v>6748402</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10622,7 +10627,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10632,7 +10637,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10658,13 +10663,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543040</t>
+          <t>https://artportalen.se/Sighting/129543039</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129543041</v>
+        <v>129543040</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10699,10 +10704,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457854</v>
+        <v>457817</v>
       </c>
       <c r="R91" t="n">
-        <v>6748444</v>
+        <v>6748400</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10734,7 +10739,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10744,7 +10749,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10770,13 +10775,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543041</t>
+          <t>https://artportalen.se/Sighting/129543040</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129543042</v>
+        <v>129543041</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10811,10 +10816,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457922</v>
+        <v>457854</v>
       </c>
       <c r="R92" t="n">
-        <v>6748447</v>
+        <v>6748444</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10846,7 +10851,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10856,7 +10861,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10882,13 +10887,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543042</t>
+          <t>https://artportalen.se/Sighting/129543041</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129543043</v>
+        <v>129543042</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10923,7 +10928,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457927</v>
+        <v>457922</v>
       </c>
       <c r="R93" t="n">
         <v>6748447</v>
@@ -10994,13 +10999,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543043</t>
+          <t>https://artportalen.se/Sighting/129543042</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129543044</v>
+        <v>129543043</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -11035,10 +11040,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>457939</v>
+        <v>457927</v>
       </c>
       <c r="R94" t="n">
-        <v>6748453</v>
+        <v>6748447</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11070,7 +11075,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11080,7 +11085,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11106,13 +11111,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543044</t>
+          <t>https://artportalen.se/Sighting/129543043</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129543045</v>
+        <v>129543044</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -11147,10 +11152,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>457912</v>
+        <v>457939</v>
       </c>
       <c r="R95" t="n">
-        <v>6748485</v>
+        <v>6748453</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11182,7 +11187,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11192,7 +11197,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11218,13 +11223,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543045</t>
+          <t>https://artportalen.se/Sighting/129543044</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129543046</v>
+        <v>129543045</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -11259,10 +11264,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>457946</v>
+        <v>457912</v>
       </c>
       <c r="R96" t="n">
-        <v>6748493</v>
+        <v>6748485</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11294,7 +11299,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11304,7 +11309,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11330,13 +11335,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543046</t>
+          <t>https://artportalen.se/Sighting/129543045</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129543047</v>
+        <v>129543046</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -11371,10 +11376,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>457952</v>
+        <v>457946</v>
       </c>
       <c r="R97" t="n">
-        <v>6748501</v>
+        <v>6748493</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11406,7 +11411,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11416,7 +11421,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11442,13 +11447,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543047</t>
+          <t>https://artportalen.se/Sighting/129543046</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129543048</v>
+        <v>129543047</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -11483,10 +11488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>457954</v>
+        <v>457952</v>
       </c>
       <c r="R98" t="n">
-        <v>6748541</v>
+        <v>6748501</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11518,7 +11523,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11528,7 +11533,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11554,13 +11559,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543048</t>
+          <t>https://artportalen.se/Sighting/129543047</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129543049</v>
+        <v>129543048</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -11595,10 +11600,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458018</v>
+        <v>457954</v>
       </c>
       <c r="R99" t="n">
-        <v>6748602</v>
+        <v>6748541</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11630,7 +11635,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11640,7 +11645,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11666,13 +11671,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543049</t>
+          <t>https://artportalen.se/Sighting/129543048</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129543050</v>
+        <v>129543049</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -11707,10 +11712,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458067</v>
+        <v>458018</v>
       </c>
       <c r="R100" t="n">
-        <v>6748648</v>
+        <v>6748602</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11742,7 +11747,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11752,7 +11757,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11778,13 +11783,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543050</t>
+          <t>https://artportalen.se/Sighting/129543049</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129543051</v>
+        <v>129543050</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11819,10 +11824,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458077</v>
+        <v>458067</v>
       </c>
       <c r="R101" t="n">
-        <v>6748657</v>
+        <v>6748648</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11890,13 +11895,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543051</t>
+          <t>https://artportalen.se/Sighting/129543050</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129543052</v>
+        <v>129543051</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11931,10 +11936,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458081</v>
+        <v>458077</v>
       </c>
       <c r="R102" t="n">
-        <v>6748667</v>
+        <v>6748657</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11966,7 +11971,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11976,7 +11981,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12002,13 +12007,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543052</t>
+          <t>https://artportalen.se/Sighting/129543051</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129543053</v>
+        <v>129543052</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -12043,7 +12048,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458094</v>
+        <v>458081</v>
       </c>
       <c r="R103" t="n">
         <v>6748667</v>
@@ -12078,7 +12083,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12088,7 +12093,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12114,13 +12119,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543053</t>
+          <t>https://artportalen.se/Sighting/129543052</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129543054</v>
+        <v>129543053</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -12155,10 +12160,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458097</v>
+        <v>458094</v>
       </c>
       <c r="R104" t="n">
-        <v>6748662</v>
+        <v>6748667</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12226,13 +12231,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543054</t>
+          <t>https://artportalen.se/Sighting/129543053</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129543055</v>
+        <v>129543054</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -12267,10 +12272,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458111</v>
+        <v>458097</v>
       </c>
       <c r="R105" t="n">
-        <v>6748654</v>
+        <v>6748662</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12302,7 +12307,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12312,7 +12317,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12338,13 +12343,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543055</t>
+          <t>https://artportalen.se/Sighting/129543054</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129543056</v>
+        <v>129543055</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -12379,10 +12384,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>458120</v>
+        <v>458111</v>
       </c>
       <c r="R106" t="n">
-        <v>6748624</v>
+        <v>6748654</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12414,7 +12419,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12424,7 +12429,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12450,13 +12455,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543056</t>
+          <t>https://artportalen.se/Sighting/129543055</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129543057</v>
+        <v>129543056</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -12491,10 +12496,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>458134</v>
+        <v>458120</v>
       </c>
       <c r="R107" t="n">
-        <v>6748614</v>
+        <v>6748624</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12562,13 +12567,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543057</t>
+          <t>https://artportalen.se/Sighting/129543056</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129543058</v>
+        <v>129543057</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12603,10 +12608,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>458143</v>
+        <v>458134</v>
       </c>
       <c r="R108" t="n">
-        <v>6748611</v>
+        <v>6748614</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12674,13 +12679,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543058</t>
+          <t>https://artportalen.se/Sighting/129543057</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129543059</v>
+        <v>129543058</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12715,10 +12720,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458174</v>
+        <v>458143</v>
       </c>
       <c r="R109" t="n">
-        <v>6748599</v>
+        <v>6748611</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12750,7 +12755,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12760,7 +12765,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12786,13 +12791,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543059</t>
+          <t>https://artportalen.se/Sighting/129543058</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129543060</v>
+        <v>129543059</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12827,10 +12832,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458177</v>
+        <v>458174</v>
       </c>
       <c r="R110" t="n">
-        <v>6748587</v>
+        <v>6748599</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12862,7 +12867,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12872,7 +12877,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12898,13 +12903,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543060</t>
+          <t>https://artportalen.se/Sighting/129543059</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129543061</v>
+        <v>129543060</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12939,10 +12944,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458155</v>
+        <v>458177</v>
       </c>
       <c r="R111" t="n">
-        <v>6748548</v>
+        <v>6748587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12974,7 +12979,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12984,7 +12989,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13010,13 +13015,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543061</t>
+          <t>https://artportalen.se/Sighting/129543060</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129543062</v>
+        <v>129543061</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -13051,10 +13056,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458140</v>
+        <v>458155</v>
       </c>
       <c r="R112" t="n">
-        <v>6748536</v>
+        <v>6748548</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13086,7 +13091,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13096,7 +13101,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13122,13 +13127,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543062</t>
+          <t>https://artportalen.se/Sighting/129543061</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129543063</v>
+        <v>129543062</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -13163,10 +13168,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458116</v>
+        <v>458140</v>
       </c>
       <c r="R113" t="n">
-        <v>6748548</v>
+        <v>6748536</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13198,7 +13203,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13208,7 +13213,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13234,13 +13239,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543063</t>
+          <t>https://artportalen.se/Sighting/129543062</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129543064</v>
+        <v>129543063</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -13275,10 +13280,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458049</v>
+        <v>458116</v>
       </c>
       <c r="R114" t="n">
-        <v>6748509</v>
+        <v>6748548</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13310,7 +13315,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13320,7 +13325,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13346,13 +13351,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543064</t>
+          <t>https://artportalen.se/Sighting/129543063</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129543065</v>
+        <v>129543064</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -13387,10 +13392,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458039</v>
+        <v>458049</v>
       </c>
       <c r="R115" t="n">
-        <v>6748504</v>
+        <v>6748509</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13458,13 +13463,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543065</t>
+          <t>https://artportalen.se/Sighting/129543064</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129543066</v>
+        <v>129543065</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -13499,10 +13504,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458042</v>
+        <v>458039</v>
       </c>
       <c r="R116" t="n">
-        <v>6748499</v>
+        <v>6748504</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13570,13 +13575,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543066</t>
+          <t>https://artportalen.se/Sighting/129543065</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129543067</v>
+        <v>129543066</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -13611,10 +13616,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457946</v>
+        <v>458042</v>
       </c>
       <c r="R117" t="n">
-        <v>6748380</v>
+        <v>6748499</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13646,7 +13651,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13656,7 +13661,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13682,13 +13687,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543067</t>
+          <t>https://artportalen.se/Sighting/129543066</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129543068</v>
+        <v>129543067</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -13723,10 +13728,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>457935</v>
+        <v>457946</v>
       </c>
       <c r="R118" t="n">
-        <v>6748390</v>
+        <v>6748380</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13794,13 +13799,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543068</t>
+          <t>https://artportalen.se/Sighting/129543067</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129543069</v>
+        <v>129543068</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13835,10 +13840,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>457930</v>
+        <v>457935</v>
       </c>
       <c r="R119" t="n">
-        <v>6748385</v>
+        <v>6748390</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13906,13 +13911,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543069</t>
+          <t>https://artportalen.se/Sighting/129543068</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129543070</v>
+        <v>129543069</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13947,10 +13952,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>457936</v>
+        <v>457930</v>
       </c>
       <c r="R120" t="n">
-        <v>6748379</v>
+        <v>6748385</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13982,7 +13987,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13992,7 +13997,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14018,13 +14023,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543070</t>
+          <t>https://artportalen.se/Sighting/129543069</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129543071</v>
+        <v>129543070</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -14059,10 +14064,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>457928</v>
+        <v>457936</v>
       </c>
       <c r="R121" t="n">
-        <v>6748344</v>
+        <v>6748379</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14094,7 +14099,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14104,7 +14109,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14130,13 +14135,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543071</t>
+          <t>https://artportalen.se/Sighting/129543070</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129543072</v>
+        <v>129543071</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -14171,10 +14176,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>457899</v>
+        <v>457928</v>
       </c>
       <c r="R122" t="n">
-        <v>6748357</v>
+        <v>6748344</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14206,7 +14211,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14216,7 +14221,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14242,13 +14247,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543072</t>
+          <t>https://artportalen.se/Sighting/129543071</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129543073</v>
+        <v>129543072</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -14283,10 +14288,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>457917</v>
+        <v>457899</v>
       </c>
       <c r="R123" t="n">
-        <v>6748303</v>
+        <v>6748357</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14318,7 +14323,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14328,7 +14333,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14354,13 +14359,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543073</t>
+          <t>https://artportalen.se/Sighting/129543072</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129543074</v>
+        <v>129543073</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -14395,10 +14400,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>457905</v>
+        <v>457917</v>
       </c>
       <c r="R124" t="n">
-        <v>6748321</v>
+        <v>6748303</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14466,13 +14471,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543074</t>
+          <t>https://artportalen.se/Sighting/129543073</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129543075</v>
+        <v>129543074</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -14507,10 +14512,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>457896</v>
+        <v>457905</v>
       </c>
       <c r="R125" t="n">
-        <v>6748336</v>
+        <v>6748321</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14542,7 +14547,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14552,7 +14557,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14578,13 +14583,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543075</t>
+          <t>https://artportalen.se/Sighting/129543074</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129543076</v>
+        <v>129543075</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -14619,10 +14624,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>457917</v>
+        <v>457896</v>
       </c>
       <c r="R126" t="n">
-        <v>6748390</v>
+        <v>6748336</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14654,7 +14659,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14664,7 +14669,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14690,13 +14695,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543076</t>
+          <t>https://artportalen.se/Sighting/129543075</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129543077</v>
+        <v>129543076</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -14731,10 +14736,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>457938</v>
+        <v>457917</v>
       </c>
       <c r="R127" t="n">
-        <v>6748409</v>
+        <v>6748390</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14766,7 +14771,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14776,7 +14781,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14802,13 +14807,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543077</t>
+          <t>https://artportalen.se/Sighting/129543076</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129543078</v>
+        <v>129543077</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -14843,10 +14848,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>457875</v>
+        <v>457938</v>
       </c>
       <c r="R128" t="n">
-        <v>6748394</v>
+        <v>6748409</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14878,7 +14883,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14888,7 +14893,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14914,38 +14919,38 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543078</t>
+          <t>https://artportalen.se/Sighting/129543077</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129542961</v>
+        <v>129543078</v>
       </c>
       <c r="B129" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14955,10 +14960,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>457859</v>
+        <v>457875</v>
       </c>
       <c r="R129" t="n">
-        <v>6748231</v>
+        <v>6748394</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14990,7 +14995,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15000,7 +15005,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15026,13 +15031,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542961</t>
+          <t>https://artportalen.se/Sighting/129543078</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129542962</v>
+        <v>129542961</v>
       </c>
       <c r="B130" t="n">
         <v>79084</v>
@@ -15067,10 +15072,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>457762</v>
+        <v>457859</v>
       </c>
       <c r="R130" t="n">
-        <v>6748208</v>
+        <v>6748231</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15102,7 +15107,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15112,7 +15117,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15138,13 +15143,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542962</t>
+          <t>https://artportalen.se/Sighting/129542961</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129542963</v>
+        <v>129542962</v>
       </c>
       <c r="B131" t="n">
         <v>79084</v>
@@ -15179,10 +15184,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>457754</v>
+        <v>457762</v>
       </c>
       <c r="R131" t="n">
-        <v>6748230</v>
+        <v>6748208</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15214,7 +15219,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15224,7 +15229,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15250,13 +15255,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542963</t>
+          <t>https://artportalen.se/Sighting/129542962</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129542964</v>
+        <v>129542963</v>
       </c>
       <c r="B132" t="n">
         <v>79084</v>
@@ -15291,10 +15296,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>457767</v>
+        <v>457754</v>
       </c>
       <c r="R132" t="n">
-        <v>6748250</v>
+        <v>6748230</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15326,7 +15331,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15336,7 +15341,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15362,13 +15367,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542964</t>
+          <t>https://artportalen.se/Sighting/129542963</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129542965</v>
+        <v>129542964</v>
       </c>
       <c r="B133" t="n">
         <v>79084</v>
@@ -15403,10 +15408,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>457760</v>
+        <v>457767</v>
       </c>
       <c r="R133" t="n">
-        <v>6748255</v>
+        <v>6748250</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15438,7 +15443,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15448,7 +15453,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15474,13 +15479,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542965</t>
+          <t>https://artportalen.se/Sighting/129542964</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129542966</v>
+        <v>129542965</v>
       </c>
       <c r="B134" t="n">
         <v>79084</v>
@@ -15515,10 +15520,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>457938</v>
+        <v>457760</v>
       </c>
       <c r="R134" t="n">
-        <v>6748466</v>
+        <v>6748255</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15550,7 +15555,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15560,7 +15565,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15586,13 +15591,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542966</t>
+          <t>https://artportalen.se/Sighting/129542965</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129542967</v>
+        <v>129542966</v>
       </c>
       <c r="B135" t="n">
         <v>79084</v>
@@ -15627,10 +15632,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>457939</v>
+        <v>457938</v>
       </c>
       <c r="R135" t="n">
-        <v>6748494</v>
+        <v>6748466</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15662,7 +15667,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15672,7 +15677,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15698,13 +15703,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542967</t>
+          <t>https://artportalen.se/Sighting/129542966</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129542968</v>
+        <v>129542967</v>
       </c>
       <c r="B136" t="n">
         <v>79084</v>
@@ -15739,10 +15744,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>458060</v>
+        <v>457939</v>
       </c>
       <c r="R136" t="n">
-        <v>6748629</v>
+        <v>6748494</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15774,7 +15779,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15784,7 +15789,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15810,16 +15815,16 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542968</t>
+          <t>https://artportalen.se/Sighting/129542967</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129542913</v>
+        <v>129542968</v>
       </c>
       <c r="B137" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15827,21 +15832,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15851,10 +15856,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>457761</v>
+        <v>458060</v>
       </c>
       <c r="R137" t="n">
-        <v>6748133</v>
+        <v>6748629</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15886,7 +15891,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15896,7 +15901,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15922,13 +15927,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542913</t>
+          <t>https://artportalen.se/Sighting/129542968</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129542914</v>
+        <v>129542913</v>
       </c>
       <c r="B138" t="n">
         <v>79946</v>
@@ -15963,10 +15968,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>457650</v>
+        <v>457761</v>
       </c>
       <c r="R138" t="n">
-        <v>6748064</v>
+        <v>6748133</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15998,7 +16003,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16008,7 +16013,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16034,13 +16039,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542914</t>
+          <t>https://artportalen.se/Sighting/129542913</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129542915</v>
+        <v>129542914</v>
       </c>
       <c r="B139" t="n">
         <v>79946</v>
@@ -16075,10 +16080,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>457754</v>
+        <v>457650</v>
       </c>
       <c r="R139" t="n">
-        <v>6748230</v>
+        <v>6748064</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16110,7 +16115,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16120,7 +16125,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16146,13 +16151,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542915</t>
+          <t>https://artportalen.se/Sighting/129542914</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129542916</v>
+        <v>129542915</v>
       </c>
       <c r="B140" t="n">
         <v>79946</v>
@@ -16187,10 +16192,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>457750</v>
+        <v>457754</v>
       </c>
       <c r="R140" t="n">
-        <v>6748276</v>
+        <v>6748230</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16222,7 +16227,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16232,7 +16237,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16258,56 +16263,51 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542916</t>
+          <t>https://artportalen.se/Sighting/129542915</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129542933</v>
+        <v>129542916</v>
       </c>
       <c r="B141" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>457753</v>
+        <v>457750</v>
       </c>
       <c r="R141" t="n">
-        <v>6748178</v>
+        <v>6748276</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16375,13 +16375,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542933</t>
+          <t>https://artportalen.se/Sighting/129542916</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129542934</v>
+        <v>129542933</v>
       </c>
       <c r="B142" t="n">
         <v>57950</v>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>457986</v>
+        <v>457753</v>
       </c>
       <c r="R142" t="n">
-        <v>6748597</v>
+        <v>6748178</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16492,13 +16492,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542934</t>
+          <t>https://artportalen.se/Sighting/129542933</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129542935</v>
+        <v>129542934</v>
       </c>
       <c r="B143" t="n">
         <v>57950</v>
@@ -16538,10 +16538,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>458060</v>
+        <v>457986</v>
       </c>
       <c r="R143" t="n">
-        <v>6748631</v>
+        <v>6748597</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16609,13 +16609,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542935</t>
+          <t>https://artportalen.se/Sighting/129542934</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129542936</v>
+        <v>129542935</v>
       </c>
       <c r="B144" t="n">
         <v>57950</v>
@@ -16655,10 +16655,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>458155</v>
+        <v>458060</v>
       </c>
       <c r="R144" t="n">
-        <v>6748562</v>
+        <v>6748631</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16690,7 +16690,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16726,16 +16726,16 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542936</t>
+          <t>https://artportalen.se/Sighting/129542935</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129542925</v>
+        <v>129542936</v>
       </c>
       <c r="B145" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16743,27 +16743,27 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>457896</v>
+        <v>458155</v>
       </c>
       <c r="R145" t="n">
-        <v>6748335</v>
+        <v>6748562</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16817,7 +16817,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16843,16 +16843,16 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542925</t>
+          <t>https://artportalen.se/Sighting/129542936</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129543111</v>
+        <v>129542925</v>
       </c>
       <c r="B146" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16860,27 +16860,27 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16889,10 +16889,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>457665</v>
+        <v>457896</v>
       </c>
       <c r="R146" t="n">
-        <v>6748081</v>
+        <v>6748335</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16960,44 +16960,44 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129543111</t>
+          <t>https://artportalen.se/Sighting/129542925</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129542927</v>
+        <v>129543111</v>
       </c>
       <c r="B147" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>458027</v>
+        <v>457665</v>
       </c>
       <c r="R147" t="n">
-        <v>6748413</v>
+        <v>6748081</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17077,13 +17077,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542927</t>
+          <t>https://artportalen.se/Sighting/129543111</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129542928</v>
+        <v>129542927</v>
       </c>
       <c r="B148" t="n">
         <v>58114</v>
@@ -17123,10 +17123,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>457940</v>
+        <v>458027</v>
       </c>
       <c r="R148" t="n">
-        <v>6748387</v>
+        <v>6748413</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17194,44 +17194,44 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542928</t>
+          <t>https://artportalen.se/Sighting/129542927</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129542947</v>
+        <v>129542928</v>
       </c>
       <c r="B149" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17240,10 +17240,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>457929</v>
+        <v>457940</v>
       </c>
       <c r="R149" t="n">
-        <v>6748484</v>
+        <v>6748387</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17285,7 +17285,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17311,13 +17311,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542947</t>
+          <t>https://artportalen.se/Sighting/129542928</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129542948</v>
+        <v>129542947</v>
       </c>
       <c r="B150" t="n">
         <v>8455</v>
@@ -17348,7 +17348,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -17357,10 +17357,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>457777</v>
+        <v>457929</v>
       </c>
       <c r="R150" t="n">
-        <v>6748294</v>
+        <v>6748484</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17428,13 +17428,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542948</t>
+          <t>https://artportalen.se/Sighting/129542947</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129542949</v>
+        <v>129542948</v>
       </c>
       <c r="B151" t="n">
         <v>8455</v>
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>457627</v>
+        <v>457777</v>
       </c>
       <c r="R151" t="n">
-        <v>6748161</v>
+        <v>6748294</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17545,13 +17545,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542949</t>
+          <t>https://artportalen.se/Sighting/129542948</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129542950</v>
+        <v>129542949</v>
       </c>
       <c r="B152" t="n">
         <v>8455</v>
@@ -17591,10 +17591,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>457695</v>
+        <v>457627</v>
       </c>
       <c r="R152" t="n">
-        <v>6748215</v>
+        <v>6748161</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17626,7 +17626,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17662,13 +17662,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542950</t>
+          <t>https://artportalen.se/Sighting/129542949</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129542951</v>
+        <v>129542950</v>
       </c>
       <c r="B153" t="n">
         <v>8455</v>
@@ -17708,10 +17708,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>457817</v>
+        <v>457695</v>
       </c>
       <c r="R153" t="n">
-        <v>6748352</v>
+        <v>6748215</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17743,7 +17743,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17779,13 +17779,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542951</t>
+          <t>https://artportalen.se/Sighting/129542950</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129542952</v>
+        <v>129542951</v>
       </c>
       <c r="B154" t="n">
         <v>8455</v>
@@ -17825,10 +17825,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>458156</v>
+        <v>457817</v>
       </c>
       <c r="R154" t="n">
-        <v>6748545</v>
+        <v>6748352</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17860,7 +17860,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17896,48 +17896,44 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542952</t>
+          <t>https://artportalen.se/Sighting/129542951</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129542969</v>
+        <v>129542952</v>
       </c>
       <c r="B155" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17946,10 +17942,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>457879</v>
+        <v>458156</v>
       </c>
       <c r="R155" t="n">
-        <v>6748454</v>
+        <v>6748545</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17981,7 +17977,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17991,7 +17987,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18017,16 +18013,16 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542969</t>
+          <t>https://artportalen.se/Sighting/129542952</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129542944</v>
+        <v>137251126</v>
       </c>
       <c r="B156" t="n">
-        <v>97989</v>
+        <v>8464</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18034,34 +18030,39 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221941</v>
+        <v>106545</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>457654</v>
+        <v>457932</v>
       </c>
       <c r="R156" t="n">
-        <v>6748070</v>
+        <v>6748548</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18088,22 +18089,22 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18129,51 +18130,60 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542944</t>
+          <t>https://artportalen.se/Sighting/137251126</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129542945</v>
+        <v>129542969</v>
       </c>
       <c r="B157" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>457654</v>
+        <v>457879</v>
       </c>
       <c r="R157" t="n">
-        <v>6748079</v>
+        <v>6748454</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18205,7 +18215,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18215,7 +18225,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18241,16 +18251,16 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542945</t>
+          <t>https://artportalen.se/Sighting/129542969</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129542939</v>
+        <v>129542944</v>
       </c>
       <c r="B158" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18258,16 +18268,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -18282,10 +18292,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>457660</v>
+        <v>457654</v>
       </c>
       <c r="R158" t="n">
-        <v>6748092</v>
+        <v>6748070</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18317,7 +18327,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18327,7 +18337,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18353,16 +18363,16 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542939</t>
+          <t>https://artportalen.se/Sighting/129542944</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129542940</v>
+        <v>129542945</v>
       </c>
       <c r="B159" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18370,16 +18380,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -18394,10 +18404,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>457879</v>
+        <v>457654</v>
       </c>
       <c r="R159" t="n">
-        <v>6748455</v>
+        <v>6748079</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18429,7 +18439,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18439,7 +18449,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18465,13 +18475,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542940</t>
+          <t>https://artportalen.se/Sighting/129542945</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129542941</v>
+        <v>129542939</v>
       </c>
       <c r="B160" t="n">
         <v>97983</v>
@@ -18506,10 +18516,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>457929</v>
+        <v>457660</v>
       </c>
       <c r="R160" t="n">
-        <v>6748448</v>
+        <v>6748092</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18541,7 +18551,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18551,7 +18561,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18577,13 +18587,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542941</t>
+          <t>https://artportalen.se/Sighting/129542939</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129542942</v>
+        <v>129542940</v>
       </c>
       <c r="B161" t="n">
         <v>97983</v>
@@ -18618,10 +18628,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>457951</v>
+        <v>457879</v>
       </c>
       <c r="R161" t="n">
-        <v>6748543</v>
+        <v>6748455</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18653,7 +18663,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18663,7 +18673,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18689,13 +18699,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542942</t>
+          <t>https://artportalen.se/Sighting/129542940</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129542943</v>
+        <v>129542941</v>
       </c>
       <c r="B162" t="n">
         <v>97983</v>
@@ -18730,10 +18740,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>457999</v>
+        <v>457929</v>
       </c>
       <c r="R162" t="n">
-        <v>6748381</v>
+        <v>6748448</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18765,7 +18775,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18775,7 +18785,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18801,16 +18811,16 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542943</t>
+          <t>https://artportalen.se/Sighting/129542941</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129542960</v>
+        <v>129542942</v>
       </c>
       <c r="B163" t="n">
-        <v>80392</v>
+        <v>97983</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18818,21 +18828,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18842,10 +18852,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>458029</v>
+        <v>457951</v>
       </c>
       <c r="R163" t="n">
-        <v>6748413</v>
+        <v>6748543</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18877,7 +18887,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18887,12 +18897,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Rikligt på jätteasp</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18918,38 +18923,38 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542960</t>
+          <t>https://artportalen.se/Sighting/129542942</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129542929</v>
+        <v>129542943</v>
       </c>
       <c r="B164" t="n">
-        <v>79350</v>
+        <v>97983</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>260591</v>
+        <v>221945</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18959,10 +18964,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>457667</v>
+        <v>457999</v>
       </c>
       <c r="R164" t="n">
-        <v>6748066</v>
+        <v>6748381</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18994,7 +18999,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19004,7 +19009,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19030,38 +19035,38 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542929</t>
+          <t>https://artportalen.se/Sighting/129542943</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129542930</v>
+        <v>129542960</v>
       </c>
       <c r="B165" t="n">
-        <v>79350</v>
+        <v>80392</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>260591</v>
+        <v>229497</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19071,10 +19076,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>457848</v>
+        <v>458029</v>
       </c>
       <c r="R165" t="n">
-        <v>6748326</v>
+        <v>6748413</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19106,7 +19111,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19116,7 +19121,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Rikligt på jätteasp</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19142,13 +19152,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129542930</t>
+          <t>https://artportalen.se/Sighting/129542960</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129542931</v>
+        <v>129542929</v>
       </c>
       <c r="B166" t="n">
         <v>79350</v>
@@ -19183,10 +19193,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>458114</v>
+        <v>457667</v>
       </c>
       <c r="R166" t="n">
-        <v>6748546</v>
+        <v>6748066</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19218,7 +19228,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19228,7 +19238,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19253,6 +19263,230 @@
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129542929</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>129542930</v>
+      </c>
+      <c r="B167" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Öndalsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>457848</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6748326</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129542930</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>129542931</v>
+      </c>
+      <c r="B168" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Öndalsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>458114</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6748546</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129542931</t>
         </is>
@@ -19425,6 +19659,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -18048,11 +18048,7 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Öndalsberget, Dlr</t>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3605,7 +3605,7 @@
         <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>137251126</v>
       </c>
       <c r="B156" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3605,7 +3605,7 @@
         <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>79608</v>
+        <v>79611</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3605,7 +3605,7 @@
         <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>79611</v>
+        <v>79616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3605,7 +3605,7 @@
         <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>79616</v>
+        <v>79627</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3605,7 +3605,7 @@
         <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>79627</v>
+        <v>79628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3605,7 +3605,7 @@
         <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>79628</v>
+        <v>79630</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47866-2025 artfynd.xlsx
+++ b/artfynd/A 47866-2025 artfynd.xlsx
@@ -3605,7 +3605,7 @@
         <v>137251099</v>
       </c>
       <c r="B28" t="n">
-        <v>79630</v>
+        <v>79634</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
